--- a/rules/CORE-000102/positive/01/data/unit-test-coreid-CG0428-positive.xlsx
+++ b/rules/CORE-000102/positive/01/data/unit-test-coreid-CG0428-positive.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,6 +118,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -662,111 +665,111 @@
           <t>AETERM</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>AETOX</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>AETOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Reported Term for the Adverse Event</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -822,19 +825,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VOMITING</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>CTCAE 4.03</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+          <t>NAUSEA</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -876,111 +871,111 @@
           <t>MHTERM</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>MHTOX</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>MHTOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Reported Term for the Medical History</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1036,19 +1031,11 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Soft Tissue Damage</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>CTCAE 4.03</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+          <t>Fracture</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1090,111 +1077,111 @@
           <t>CETERM</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>CETOX</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>CETOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Reported Term for the Clinical Event</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1250,19 +1237,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Edema</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>CTCAE 4.03</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+          <t>Migraine</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1319,150 +1298,150 @@
           <t>EGORRESU</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>EGTOX</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>EGTOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>ECG Test or Examination Short Name</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>ECG Test or Examination Name</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Result or Finding in Original Units</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Original Units</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1531,32 +1510,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>QTAG</t>
+          <t>QRSAG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>QT Interval, Aggregate</t>
+          <t>PR Interval, Aggregate</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>221</v>
+        <v>0.362</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>msec</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CTCAE 4.03</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+          <t>sec</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1613,150 +1584,150 @@
           <t>LBORRESU</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>LBTOX</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>LBTOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Lab Test or Examination Short Name</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Lab Test or Examination Name</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Result or Finding in Original Units</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Original Units</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1825,32 +1796,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GLUC</t>
+          <t>HGFR</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>HGFR</t>
+          <t>Hepatocyte Growth Factor Receptor</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>mg/dL</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>CTCAE 4.03</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+          <t>ng/mL</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1907,150 +1870,150 @@
           <t>PCORRESU</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>PCTOX</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>PCTOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Pharmacokinetic Test Short Name</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Pharmacokinetic Test Name</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Result or Finding in Original Units</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Original Units</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2128,23 +2091,15 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>ug/mL</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>NCI 4.03</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2201,150 +2156,150 @@
           <t>PPORRESU</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>PPTOX</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>PPTOXGR</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Study Identifier</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>Domain Abbreviation</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Parameter Short Name</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Parameter Name</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>Result or Finding in Original Units</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Original Units</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Toxicity</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Standard Toxicity Grade</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="J4" s="4" t="n">
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="7" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2413,32 +2368,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CMAX</t>
+          <t>TMAX</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Max Conc</t>
+          <t>Time of CMAX</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>44.5</v>
+        <v>1.87</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>ug/L</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>NCI 4.03</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>GRADE 2</t>
-        </is>
-      </c>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
